--- a/assets/constructions/examples/ctd_graver.xlsx
+++ b/assets/constructions/examples/ctd_graver.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,36 @@
           <t>mgro</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H-GS-3-15-0,50/A8WY00</t>
+          <t>H-GS-3-36-0,50/A8WY00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -634,7 +659,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
@@ -669,11 +694,22 @@
           <t>VHM</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H-GS-3-36-0,50/A8WY00</t>
+          <t>H-GR-3-36-R=0.30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -688,14 +724,14 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
@@ -714,7 +750,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A8WY00</t>
+          <t>R7WY00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -759,11 +795,22 @@
           <t>VHM</t>
         </is>
       </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H-GR-3-36-R=0.30</t>
+          <t>H-GS-3-15-0,50/A8WY00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -778,14 +825,14 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>1</v>
       </c>
@@ -804,7 +851,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>R7WY00</t>
+          <t>A8WY00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -814,7 +861,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
@@ -847,6 +894,17 @@
       <c r="AD4" t="inlineStr">
         <is>
           <t>VHM</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
